--- a/output/pdf_financials_xlsx/ALTR.P.xlsx
+++ b/output/pdf_financials_xlsx/ALTR.P.xlsx
@@ -823,19 +823,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.035107</v>
+        <v>-0.035107</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.176643</v>
+        <v>-0.176643</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.041141</v>
+        <v>-0.041141</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.048661</v>
+        <v>-0.048661</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.048154</v>
+        <v>-0.048154</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.035107</v>
+        <v>-0.035107</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.176643</v>
+        <v>-0.176643</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.041141</v>
+        <v>-0.041141</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.048661</v>
+        <v>-0.048661</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.048154</v>
+        <v>-0.048154</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -1032,19 +1032,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.035107</v>
+        <v>-0.035107</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.176643</v>
+        <v>-0.176643</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.041141</v>
+        <v>-0.041141</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.048661</v>
+        <v>-0.048661</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.048154</v>
+        <v>-0.048154</v>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1.950389</v>
+        <v>-1.950389</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2.94405</v>
+        <v>-2.94405</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2.742733</v>
+        <v>-2.742733</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>2.43305</v>
+        <v>-2.43305</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>2.4077</v>
+        <v>-2.4077</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1140,19 +1140,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.035107</v>
+        <v>-0.035107</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.176643</v>
+        <v>-0.176643</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.041141</v>
+        <v>-0.041141</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.048661</v>
+        <v>-0.048661</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.048154</v>
+        <v>-0.048154</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.035107</v>
+        <v>-0.035107</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.176643</v>
+        <v>-0.176643</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.041141</v>
+        <v>-0.041141</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.048661</v>
+        <v>-0.048661</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.048154</v>
+        <v>-0.048154</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
@@ -2860,19 +2860,19 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.106706</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.106706</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.106706</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.106706</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.074534</v>
       </c>
     </row>
     <row r="93">
@@ -4386,7 +4386,11 @@
           <t>Share-based payments reserve (Note 5)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -4614,7 +4618,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -4796,7 +4804,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -6369,10 +6381,10 @@
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.048661</v>
+        <v>-0.048661</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>0.048154</v>
+        <v>-0.048154</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -6544,13 +6556,13 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.035107</v>
+        <v>-0.035107</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.176643</v>
+        <v>-0.176643</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.041141</v>
+        <v>-0.041141</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ALTR.P.xlsx
+++ b/output/pdf_financials_xlsx/ALTR.P.xlsx
@@ -664,16 +664,16 @@
         <v>0.035107</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.053338</v>
+        <v>0.176643</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.010843</v>
+        <v>0.041141</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.016662</v>
+        <v>0.048661</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.019602</v>
+        <v>0.048154</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         <v>-0.035107</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.053338</v>
+        <v>-0.176643</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.010843</v>
+        <v>-0.041141</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.016662</v>
+        <v>-0.048661</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.019602</v>
+        <v>-0.048154</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.118874</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.07871</v>
       </c>
     </row>
     <row r="35">
@@ -1391,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.118874</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.07871</v>
       </c>
     </row>
     <row r="37">
@@ -1691,10 +1691,10 @@
         <v>0.176035</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.118874</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.07871</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">

--- a/output/pdf_financials_xlsx/ALTR.P.xlsx
+++ b/output/pdf_financials_xlsx/ALTR.P.xlsx
@@ -513,10 +513,8 @@
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -540,10 +538,8 @@
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -567,10 +563,8 @@
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -594,10 +588,8 @@
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -621,10 +613,8 @@
       <c r="F8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -648,10 +638,8 @@
       <c r="F9" s="3" t="n">
         <v>0.019602</v>
       </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G9" s="3" t="n">
+        <v>0.018602</v>
       </c>
     </row>
     <row r="10">
@@ -675,10 +663,8 @@
       <c r="F10" s="3" t="n">
         <v>0.048154</v>
       </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G10" s="3" t="n">
+        <v>0.047655</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +688,8 @@
       <c r="F11" s="3" t="n">
         <v>-0.048154</v>
       </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G11" s="3" t="n">
+        <v>-0.047655</v>
       </c>
     </row>
     <row r="12">
@@ -729,10 +713,8 @@
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -756,10 +738,8 @@
       <c r="F13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -783,10 +763,8 @@
       <c r="F14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -810,10 +788,8 @@
       <c r="F15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -837,10 +813,8 @@
       <c r="F16" s="3" t="n">
         <v>-0.048154</v>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G16" s="3" t="n">
+        <v>-0.047655</v>
       </c>
     </row>
     <row r="17">
@@ -864,10 +838,8 @@
       <c r="F17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -965,10 +937,8 @@
       <c r="F20" s="3" t="n">
         <v>-0.048154</v>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" s="3" t="n">
+        <v>-0.047655</v>
       </c>
     </row>
     <row r="21">
@@ -992,10 +962,8 @@
       <c r="F21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1019,10 +987,8 @@
       <c r="F22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1046,10 +1012,8 @@
       <c r="F23" s="3" t="n">
         <v>-0.048154</v>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G23" s="3" t="n">
+        <v>-0.047655</v>
       </c>
     </row>
     <row r="24">
@@ -1073,10 +1037,8 @@
       <c r="F24" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G24" s="3" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="25">
@@ -1100,10 +1062,8 @@
       <c r="F25" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G25" s="3" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="26">
@@ -1127,10 +1087,8 @@
       <c r="F26" s="3" t="n">
         <v>-2.4077</v>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G26" s="3" t="n">
+        <v>-2.38275</v>
       </c>
     </row>
     <row r="27">
@@ -1154,10 +1112,8 @@
       <c r="F27" s="3" t="n">
         <v>-0.048154</v>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G27" s="3" t="n">
+        <v>-0.047655</v>
       </c>
     </row>
     <row r="28">
@@ -1181,10 +1137,8 @@
       <c r="F28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1208,10 +1162,8 @@
       <c r="F29" s="3" t="n">
         <v>-0.048154</v>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G29" s="3" t="n">
+        <v>-0.047655</v>
       </c>
     </row>
     <row r="30">
@@ -1272,10 +1224,8 @@
       <c r="F31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3046,10 +2996,8 @@
       <c r="F99" s="3" t="n">
         <v>-0.048154</v>
       </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G99" s="3" t="n">
+        <v>-0.047655</v>
       </c>
     </row>
     <row r="100">
@@ -3075,10 +3023,8 @@
       <c r="F100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -3104,10 +3050,8 @@
       <c r="F101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3133,10 +3077,8 @@
       <c r="F102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3162,10 +3104,8 @@
       <c r="F103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3191,10 +3131,8 @@
       <c r="F104" s="3" t="n">
         <v>-0.009006999999999999</v>
       </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G104" s="3" t="n">
+        <v>0.002491</v>
       </c>
     </row>
     <row r="105">
@@ -3220,10 +3158,8 @@
       <c r="F105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3249,10 +3185,8 @@
       <c r="F106" s="3" t="n">
         <v>-0.009006999999999999</v>
       </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G106" s="3" t="n">
+        <v>0.002491</v>
       </c>
     </row>
     <row r="107">
@@ -3278,10 +3212,8 @@
       <c r="F107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3307,10 +3239,8 @@
       <c r="F108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3336,10 +3266,8 @@
       <c r="F109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3365,10 +3293,8 @@
       <c r="F110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3394,10 +3320,8 @@
       <c r="F111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3423,10 +3347,8 @@
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3452,10 +3374,8 @@
       <c r="F113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3481,10 +3401,8 @@
       <c r="F114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3510,10 +3428,8 @@
       <c r="F115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3539,10 +3455,8 @@
       <c r="F116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3568,10 +3482,8 @@
       <c r="F117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3597,10 +3509,8 @@
       <c r="F118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3661,10 +3571,8 @@
       <c r="F120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3690,10 +3598,8 @@
       <c r="F121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3719,10 +3625,8 @@
       <c r="F122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3748,10 +3652,8 @@
       <c r="F123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3777,10 +3679,8 @@
       <c r="F124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3806,10 +3706,8 @@
       <c r="F125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3835,10 +3733,8 @@
       <c r="F126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3901,10 +3797,8 @@
       <c r="F128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3965,10 +3859,8 @@
       <c r="F130" s="3" t="n">
         <v>0.176035</v>
       </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G130" s="3" t="n">
+        <v>0.118874</v>
       </c>
     </row>
     <row r="131">
@@ -3994,10 +3886,8 @@
       <c r="F131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4023,10 +3913,8 @@
       <c r="F132" s="3" t="n">
         <v>-0.057161</v>
       </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G132" s="3" t="n">
+        <v>-0.040164</v>
       </c>
     </row>
     <row r="133">
@@ -4052,10 +3940,8 @@
       <c r="F133" s="3" t="n">
         <v>0.118874</v>
       </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G133" s="3" t="n">
+        <v>0.07871</v>
       </c>
     </row>
     <row r="134">
@@ -4081,10 +3967,8 @@
       <c r="F134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -4110,10 +3994,8 @@
       <c r="F135" s="3" t="n">
         <v>-0.057161</v>
       </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G135" s="3" t="n">
+        <v>-0.045164</v>
       </c>
     </row>
   </sheetData>
@@ -4127,7 +4009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5087,7 +4969,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
+          <t>Net loss for the year $</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5100,22 +4982,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="5" t="n">
-        <v>-0.176643</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>-0.041141</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>-0.048661</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I21" s="5" t="n">
         <v>-0.048154</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J21" s="5" t="n">
+        <v>-0.047655</v>
       </c>
     </row>
     <row r="22">
@@ -5156,10 +5042,8 @@
       <c r="I22" s="5" t="n">
         <v>-0.009006999999999999</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J22" s="5" t="n">
+        <v>0.002491</v>
       </c>
     </row>
     <row r="23">
@@ -5200,10 +5084,8 @@
       <c r="I23" s="5" t="n">
         <v>-0.057161</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J23" s="5" t="n">
+        <v>-0.045164</v>
       </c>
     </row>
     <row r="24">
@@ -5222,7 +5104,11 @@
           <t>Shares issued in private placement</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -5246,10 +5132,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J24" s="5" t="n">
+        <v>0.005</v>
       </c>
     </row>
     <row r="25">
@@ -5290,10 +5174,8 @@
       <c r="I25" s="5" t="n">
         <v>-0.057161</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J25" s="5" t="n">
+        <v>-0.040164</v>
       </c>
     </row>
     <row r="26">
@@ -5334,10 +5216,8 @@
       <c r="I26" s="5" t="n">
         <v>0.176035</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J26" s="5" t="n">
+        <v>0.118874</v>
       </c>
     </row>
     <row r="27">
@@ -5378,10 +5258,8 @@
       <c r="I27" s="5" t="n">
         <v>0.118874</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J27" s="5" t="n">
+        <v>0.07871</v>
       </c>
     </row>
     <row r="28">
@@ -5392,17 +5270,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Net loss for the period $</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5411,22 +5289,16 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.080003</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.176643</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.041141</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-0.048661</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>-0.048154</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -5442,17 +5314,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5461,7 +5333,7 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.00175</v>
+        <v>0.080003</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -5492,17 +5364,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Issuance of capital stock</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IssuanceOfCapitalStock</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5511,7 +5383,7 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.37</v>
+        <v>0.00175</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -5547,12 +5419,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
+          <t>Issuance of capital stock</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>IssuanceOfCapitalStock</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5561,7 +5433,7 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-0.04574</v>
+        <v>0.37</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -5597,12 +5469,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cash provided by financing activities</t>
+          <t>Share issuance costs</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5611,7 +5483,7 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.32426</v>
+        <v>-0.04574</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -5642,22 +5514,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Net loss for the period $ (176,643) $</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-0.035107</v>
+        <v>0.32426</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -5688,28 +5564,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Share-based compensation 80,003</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Net loss for the period $ (176,643) $</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F34" s="5" t="n">
+        <v>-0.035107</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5740,17 +5610,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (6,936)</t>
+          <t>Share-based compensation 80,003</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5758,8 +5628,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F35" s="5" t="n">
-        <v>0.012622</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5795,12 +5667,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Prepaid expenses 1,750</t>
+          <t>Accounts payable and accrued liabilities (6,936)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5809,7 +5681,7 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.002002</v>
+        <v>0.012622</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5845,17 +5717,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cash (used in) operating activities (101,826)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Prepaid expenses 1,750</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-0.024487</v>
+        <v>-0.002002</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -5886,28 +5762,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Issuance of capital stock 370,000</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>IssuanceOfCapitalStock</t>
-        </is>
-      </c>
+          <t>Cash (used in) operating activities (101,826)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F38" s="5" t="n">
+        <v>-0.024487</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -5943,10 +5813,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Share issuance costs (45,740)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Issuance of capital stock 370,000</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -5991,14 +5865,10 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cash provided by financing activities 324,260</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Share issuance costs (45,740)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -6043,12 +5913,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net change in cash 222,434</t>
+          <t>Cash provided by financing activities 324,260</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6056,8 +5926,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F41" s="5" t="n">
-        <v>-0.024487</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -6093,12 +5965,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cash, beginning of year 31,684</t>
+          <t>Net change in cash 222,434</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -6107,7 +5979,7 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.056171</v>
+        <v>-0.024487</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -6143,12 +6015,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cash, end of year $ 254,118 $</t>
+          <t>Cash, beginning of year 31,684</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6157,7 +6029,7 @@
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.031684</v>
+        <v>0.056171</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -6183,38 +6055,46 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Legal $</t>
+          <t>Cash, end of year $ 254,118 $</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>0.035107</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.053338</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.010843</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>0.016662</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>0.019602</v>
+        <v>0.031684</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -6235,31 +6115,31 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Audit and accounting</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Legal $</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.035107</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.024195</v>
+        <v>0.053338</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.016868</v>
+        <v>0.010843</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.019009</v>
+        <v>0.016662</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>0.017497</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019602</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>0.018602</v>
       </c>
     </row>
     <row r="46">
@@ -6275,7 +6155,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Operating</t>
+          <t>Audit and accounting</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -6285,21 +6165,19 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.019107</v>
+        <v>0.024195</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.01343</v>
+        <v>0.016868</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0.01299</v>
+        <v>0.019009</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>0.011055</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.017497</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>0.017551</v>
       </c>
     </row>
     <row r="47">
@@ -6315,33 +6193,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>0.035107</v>
+          <t>Operating</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.176643</v>
+        <v>0.019107</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.041141</v>
+        <v>0.01343</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>0.048661</v>
+        <v>0.01299</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>0.048154</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.011055</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>0.011502</v>
       </c>
     </row>
     <row r="48">
@@ -6357,39 +6231,31 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.035107</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.176643</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.041141</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>-0.048661</v>
+        <v>0.048661</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>-0.048154</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.048154</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0.047655</v>
       </c>
     </row>
     <row r="49">
@@ -6405,12 +6271,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Net loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6429,15 +6295,13 @@
         </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>2e-08</v>
+        <v>-0.048661</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>2e-08</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.048154</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>-0.047655</v>
       </c>
     </row>
     <row r="50">
@@ -6453,12 +6317,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding (Note 5)</t>
+          <t>Basic and diluted loss per share $</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6477,15 +6341,13 @@
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>2.75</v>
+        <v>2e-08</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2e-08</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>2e-08</v>
       </c>
     </row>
     <row r="51">
@@ -6501,37 +6363,37 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding (Note 5)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>0.080003</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H51" s="5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="52">
@@ -6542,27 +6404,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>-0.035107</v>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>-0.176643</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-0.041141</v>
+        <v>0.080003</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -6593,22 +6455,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Basic and dilute loss per share $</t>
+          <t>Net loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1.8e-08</v>
+        <v>-0.035107</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>5.999999999999999e-08</v>
+        <v>-0.176643</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>1.5e-08</v>
+        <v>-0.041141</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -6634,39 +6496,85 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>Net loss and comprehensive loss for</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Basic and dilute loss per share $</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>1.8e-08</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>5.999999999999999e-08</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>1.5e-08</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>Weighted average number of</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Weighted average number of shares outstanding (Note 5)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>BasicAverageShares</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="E55" s="5" t="n">
         <v>2.001281</v>
       </c>
-      <c r="F54" s="5" t="n">
+      <c r="F55" s="5" t="n">
         <v>2.946581</v>
       </c>
-      <c r="G54" s="5" t="n">
+      <c r="G55" s="5" t="n">
         <v>2.75</v>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
